--- a/AAII_Financials/Yearly/DSS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DSS_YR_FIN.xlsx
@@ -1062,7 +1062,7 @@
         <v>2900</v>
       </c>
       <c r="E15" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="F15" s="3">
         <v>5200</v>
@@ -1305,7 +1305,7 @@
         <v>-11500</v>
       </c>
       <c r="E21" s="3">
-        <v>-43800</v>
+        <v>-43700</v>
       </c>
       <c r="F21" s="3">
         <v>-48900</v>
@@ -4093,7 +4093,7 @@
         <v>2400</v>
       </c>
       <c r="E83" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="F83" s="3">
         <v>2900</v>
